--- a/doma.xlsx
+++ b/doma.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Альфия\Desktop\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B32FC774-C0B5-407F-A4E6-3C8B166F44C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0DDDCAE6-B60F-40EE-BB37-A0874639C038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Исправления координат" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="52">
   <si>
     <t>№</t>
   </si>
@@ -137,17 +138,67 @@
   <si>
     <t>Сююмбике</t>
   </si>
+  <si>
+    <t>Строка Excel</t>
+  </si>
+  <si>
+    <t>Комментарий</t>
+  </si>
+  <si>
+    <t>Кайманова 11</t>
+  </si>
+  <si>
+    <t>Исправлено: дом в г. Нижнекамск</t>
+  </si>
+  <si>
+    <t>Гагарина 2</t>
+  </si>
+  <si>
+    <t>Гагарина 4</t>
+  </si>
+  <si>
+    <t>Гагарина 8</t>
+  </si>
+  <si>
+    <t>Спортивная 21</t>
+  </si>
+  <si>
+    <t>Гагарина 18</t>
+  </si>
+  <si>
+    <t>Гагарина 20</t>
+  </si>
+  <si>
+    <t>Гагарина 22</t>
+  </si>
+  <si>
+    <t>Мира 3</t>
+  </si>
+  <si>
+    <t>Мира 5</t>
+  </si>
+  <si>
+    <t>Мира 7</t>
+  </si>
+  <si>
+    <t>Мира 17</t>
+  </si>
+  <si>
+    <t>Мира 6</t>
+  </si>
+  <si>
+    <t>Мира 8</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Carlito"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -159,8 +210,14 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -170,19 +227,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFBDD6EE"/>
-        <bgColor rgb="FFBDD6EE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E2F3"/>
-        <bgColor rgb="FFD9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -213,7 +272,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -263,6 +322,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -278,10 +338,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -325,97 +381,48 @@
         <a:srgbClr val="0563C1"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Carlito"/>
-        <a:ea typeface="Carlito"/>
-        <a:cs typeface="Carlito"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Carlito"/>
-        <a:ea typeface="Carlito"/>
-        <a:cs typeface="Carlito"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Sheets">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="dk1"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -445,22 +452,22 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -482,20 +489,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="4" style="12" customWidth="1"/>
+    <col min="1" max="1" width="3.5" style="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.375" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.25" style="12" customWidth="1"/>
-    <col min="4" max="4" width="9.875" style="12" customWidth="1"/>
-    <col min="5" max="5" width="10" style="12" customWidth="1"/>
-    <col min="6" max="6" width="8.375" style="12" customWidth="1"/>
-    <col min="7" max="8" width="9.125" style="12" customWidth="1"/>
-    <col min="9" max="9" width="27.375" style="12" customWidth="1"/>
+    <col min="3" max="3" width="7.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.75" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="32.375" style="12" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25.625" style="12" customWidth="1"/>
     <col min="11" max="26" width="8.625" style="12" customWidth="1"/>
     <col min="27" max="16384" width="12.625" style="12"/>
@@ -547,7 +551,7 @@
       <c r="Y1" s="4"/>
       <c r="Z1" s="4"/>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:26" ht="15">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -594,7 +598,7 @@
       <c r="Y2" s="4"/>
       <c r="Z2" s="4"/>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:26" ht="15">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -641,7 +645,7 @@
       <c r="Y3" s="4"/>
       <c r="Z3" s="4"/>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:26" ht="15">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -688,7 +692,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:26" ht="15">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -735,7 +739,7 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:26" ht="15">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -782,7 +786,7 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:26" ht="15">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -829,7 +833,7 @@
       <c r="Y7" s="4"/>
       <c r="Z7" s="4"/>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:26" ht="15">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -876,7 +880,7 @@
       <c r="Y8" s="4"/>
       <c r="Z8" s="4"/>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:26" ht="15">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -923,7 +927,7 @@
       <c r="Y9" s="4"/>
       <c r="Z9" s="4"/>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:26" ht="15">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -970,7 +974,7 @@
       <c r="Y10" s="4"/>
       <c r="Z10" s="4"/>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:26" ht="15">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1017,7 +1021,7 @@
       <c r="Y11" s="4"/>
       <c r="Z11" s="4"/>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:26" ht="15">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1064,7 +1068,7 @@
       <c r="Y12" s="4"/>
       <c r="Z12" s="4"/>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:26" ht="15">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1111,7 +1115,7 @@
       <c r="Y13" s="4"/>
       <c r="Z13" s="4"/>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:26" ht="15">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1158,7 +1162,7 @@
       <c r="Y14" s="4"/>
       <c r="Z14" s="4"/>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:26" ht="15">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1205,7 +1209,7 @@
       <c r="Y15" s="4"/>
       <c r="Z15" s="4"/>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:26" ht="15">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1252,7 +1256,7 @@
       <c r="Y16" s="4"/>
       <c r="Z16" s="4"/>
     </row>
-    <row r="17" spans="1:26">
+    <row r="17" spans="1:26" ht="15">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1299,7 +1303,7 @@
       <c r="Y17" s="4"/>
       <c r="Z17" s="4"/>
     </row>
-    <row r="18" spans="1:26">
+    <row r="18" spans="1:26" ht="15">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1346,7 +1350,7 @@
       <c r="Y18" s="4"/>
       <c r="Z18" s="4"/>
     </row>
-    <row r="19" spans="1:26">
+    <row r="19" spans="1:26" ht="15">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1393,7 +1397,7 @@
       <c r="Y19" s="4"/>
       <c r="Z19" s="4"/>
     </row>
-    <row r="20" spans="1:26">
+    <row r="20" spans="1:26" ht="15">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -2729,10 +2733,10 @@
         <v>243</v>
       </c>
       <c r="G48" s="3">
-        <v>55.654566000000003</v>
+        <v>55.656787999999999</v>
       </c>
       <c r="H48" s="3">
-        <v>51.968018499999999</v>
+        <v>51.845826000000002</v>
       </c>
       <c r="I48" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2776,10 +2780,10 @@
         <v>156</v>
       </c>
       <c r="G49" s="3">
-        <v>55.654699200000003</v>
+        <v>55.640233000000002</v>
       </c>
       <c r="H49" s="3">
-        <v>51.963070000000002</v>
+        <v>51.836852</v>
       </c>
       <c r="I49" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2823,10 +2827,10 @@
         <v>183</v>
       </c>
       <c r="G50" s="3">
-        <v>55.654851800000003</v>
+        <v>55.641620000000003</v>
       </c>
       <c r="H50" s="3">
-        <v>51.962783299999998</v>
+        <v>51.837966000000002</v>
       </c>
       <c r="I50" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2870,10 +2874,10 @@
         <v>109</v>
       </c>
       <c r="G51" s="3">
-        <v>55.655243900000002</v>
+        <v>55.643560999999998</v>
       </c>
       <c r="H51" s="3">
-        <v>51.962730499999999</v>
+        <v>51.839871000000002</v>
       </c>
       <c r="I51" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2917,10 +2921,10 @@
         <v>178</v>
       </c>
       <c r="G52" s="3">
-        <v>55.743800399999998</v>
+        <v>55.639156</v>
       </c>
       <c r="H52" s="3">
-        <v>51.990945199999999</v>
+        <v>51.840212000000001</v>
       </c>
       <c r="I52" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3246,10 +3250,10 @@
         <v>62</v>
       </c>
       <c r="G59" s="3">
-        <v>55.656716000000003</v>
+        <v>55.64696</v>
       </c>
       <c r="H59" s="3">
-        <v>51.964271199999999</v>
+        <v>51.845861999999997</v>
       </c>
       <c r="I59" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3293,10 +3297,10 @@
         <v>62</v>
       </c>
       <c r="G60" s="3">
-        <v>55.656908700000002</v>
+        <v>55.647590000000001</v>
       </c>
       <c r="H60" s="3">
-        <v>51.964476599999998</v>
+        <v>51.845852999999998</v>
       </c>
       <c r="I60" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3340,10 +3344,10 @@
         <v>62</v>
       </c>
       <c r="G61" s="3">
-        <v>55.657127699999997</v>
+        <v>55.647097000000002</v>
       </c>
       <c r="H61" s="3">
-        <v>51.9646981</v>
+        <v>51.847209999999997</v>
       </c>
       <c r="I61" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3387,10 +3391,10 @@
         <v>198</v>
       </c>
       <c r="G62" s="3">
-        <v>55.737194299999999</v>
+        <v>55.651947999999997</v>
       </c>
       <c r="H62" s="3">
-        <v>51.916841599999998</v>
+        <v>51.818337999999997</v>
       </c>
       <c r="I62" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3434,10 +3438,10 @@
         <v>341</v>
       </c>
       <c r="G63" s="3">
-        <v>55.737728300000001</v>
+        <v>55.652191999999999</v>
       </c>
       <c r="H63" s="3">
-        <v>51.917247799999998</v>
+        <v>51.816406999999998</v>
       </c>
       <c r="I63" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3481,10 +3485,10 @@
         <v>144</v>
       </c>
       <c r="G64" s="3">
-        <v>55.738002199999997</v>
+        <v>55.650708999999999</v>
       </c>
       <c r="H64" s="3">
-        <v>51.917484899999998</v>
+        <v>51.817646000000003</v>
       </c>
       <c r="I64" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3528,10 +3532,10 @@
         <v>270</v>
       </c>
       <c r="G65" s="3">
-        <v>55.7397767</v>
+        <v>55.650545999999999</v>
       </c>
       <c r="H65" s="3">
-        <v>51.919174599999998</v>
+        <v>51.814807999999999</v>
       </c>
       <c r="I65" s="4" t="str">
         <f t="shared" si="0"/>
@@ -3998,10 +4002,10 @@
         <v>111</v>
       </c>
       <c r="G75" s="3">
-        <v>55.737922699999999</v>
+        <v>55.653405999999997</v>
       </c>
       <c r="H75" s="3">
-        <v>51.918099900000001</v>
+        <v>51.815634000000003</v>
       </c>
       <c r="I75" s="4" t="str">
         <f t="shared" si="0"/>
@@ -4045,10 +4049,10 @@
         <v>200</v>
       </c>
       <c r="G76" s="3">
-        <v>55.7384889</v>
+        <v>55.653334999999998</v>
       </c>
       <c r="H76" s="3">
-        <v>51.918474199999999</v>
+        <v>51.814250999999999</v>
       </c>
       <c r="I76" s="4" t="str">
         <f t="shared" si="0"/>
@@ -30454,7 +30458,277 @@
       <c r="Z1000" s="4"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15">
+      <c r="A1" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>48</v>
+      </c>
+      <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2">
+        <v>55.656787999999999</v>
+      </c>
+      <c r="D2">
+        <v>51.845826000000002</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>49</v>
+      </c>
+      <c r="B3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3">
+        <v>55.640233000000002</v>
+      </c>
+      <c r="D3">
+        <v>51.836852</v>
+      </c>
+      <c r="E3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>50</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4">
+        <v>55.641620000000003</v>
+      </c>
+      <c r="D4">
+        <v>51.837966000000002</v>
+      </c>
+      <c r="E4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>51</v>
+      </c>
+      <c r="B5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5">
+        <v>55.643560999999998</v>
+      </c>
+      <c r="D5">
+        <v>51.839871000000002</v>
+      </c>
+      <c r="E5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>52</v>
+      </c>
+      <c r="B6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6">
+        <v>55.639156</v>
+      </c>
+      <c r="D6">
+        <v>51.840212000000001</v>
+      </c>
+      <c r="E6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>59</v>
+      </c>
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7">
+        <v>55.64696</v>
+      </c>
+      <c r="D7">
+        <v>51.845861999999997</v>
+      </c>
+      <c r="E7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>60</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8">
+        <v>55.647590000000001</v>
+      </c>
+      <c r="D8">
+        <v>51.845852999999998</v>
+      </c>
+      <c r="E8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9">
+        <v>61</v>
+      </c>
+      <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9">
+        <v>55.647097000000002</v>
+      </c>
+      <c r="D9">
+        <v>51.847209999999997</v>
+      </c>
+      <c r="E9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10">
+        <v>62</v>
+      </c>
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10">
+        <v>55.651947999999997</v>
+      </c>
+      <c r="D10">
+        <v>51.818337999999997</v>
+      </c>
+      <c r="E10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>63</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11">
+        <v>55.652191999999999</v>
+      </c>
+      <c r="D11">
+        <v>51.816406999999998</v>
+      </c>
+      <c r="E11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12">
+        <v>64</v>
+      </c>
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12">
+        <v>55.650708999999999</v>
+      </c>
+      <c r="D12">
+        <v>51.817646000000003</v>
+      </c>
+      <c r="E12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13">
+        <v>65</v>
+      </c>
+      <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13">
+        <v>55.650545999999999</v>
+      </c>
+      <c r="D13">
+        <v>51.814807999999999</v>
+      </c>
+      <c r="E13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14">
+        <v>75</v>
+      </c>
+      <c r="B14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14">
+        <v>55.653405999999997</v>
+      </c>
+      <c r="D14">
+        <v>51.815634000000003</v>
+      </c>
+      <c r="E14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15">
+        <v>76</v>
+      </c>
+      <c r="B15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15">
+        <v>55.653334999999998</v>
+      </c>
+      <c r="D15">
+        <v>51.814250999999999</v>
+      </c>
+      <c r="E15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>